--- a/docs/downloads/09/t10_sources_endettement_marovoay_tous.xlsx
+++ b/docs/downloads/09/t10_sources_endettement_marovoay_tous.xlsx
@@ -405,12 +405,6 @@
           <t>Commerçants</t>
         </is>
       </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>1.9</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -477,12 +471,6 @@
           <t>Autres</t>
         </is>
       </c>
-      <c r="C7">
-        <v>4</v>
-      </c>
-      <c r="D7">
-        <v>7.4</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -495,12 +483,6 @@
           <t>Commerçants</t>
         </is>
       </c>
-      <c r="C8">
-        <v>1</v>
-      </c>
-      <c r="D8">
-        <v>1.8</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -585,12 +567,6 @@
           <t>Commerçants</t>
         </is>
       </c>
-      <c r="C13">
-        <v>1</v>
-      </c>
-      <c r="D13">
-        <v>2.2</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -657,12 +633,6 @@
           <t>Autres</t>
         </is>
       </c>
-      <c r="C17">
-        <v>1</v>
-      </c>
-      <c r="D17">
-        <v>2.9</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -675,12 +645,6 @@
           <t>Commerçants</t>
         </is>
       </c>
-      <c r="C18">
-        <v>1</v>
-      </c>
-      <c r="D18">
-        <v>2.8</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -764,12 +728,6 @@
         <is>
           <t>Commerçants</t>
         </is>
-      </c>
-      <c r="C23">
-        <v>4</v>
-      </c>
-      <c r="D23">
-        <v>2.1</v>
       </c>
     </row>
     <row r="24">

--- a/docs/downloads/09/t10_sources_endettement_marovoay_tous.xlsx
+++ b/docs/downloads/09/t10_sources_endettement_marovoay_tous.xlsx
@@ -379,7 +379,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -397,7 +397,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -409,7 +409,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -427,7 +427,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -445,7 +445,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -463,7 +463,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -475,7 +475,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -487,7 +487,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -505,7 +505,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -523,7 +523,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -541,7 +541,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -559,7 +559,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -571,7 +571,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -589,7 +589,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -607,7 +607,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -625,7 +625,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -637,7 +637,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -649,7 +649,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -667,7 +667,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -685,7 +685,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -703,7 +703,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -721,7 +721,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -733,7 +733,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -751,7 +751,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -769,7 +769,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
